--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VasilBanchev.DESKTOP-SV3I19T\Documents\Интервюта\Задачи\Diyan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED66FF4D-7077-48A6-9806-DCC532C2E45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FD8739-2BE2-4EC4-A207-43F8697EFCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{17E9812E-A6C3-44D0-9159-5F64C6DD5080}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Задача</t>
   </si>
   <si>
-    <t>ОНбординг</t>
-  </si>
-  <si>
     <t>Трело</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t xml:space="preserve">Втори проект - </t>
+  </si>
+  <si>
+    <t>Онбординг</t>
   </si>
 </sst>
 </file>
@@ -476,7 +476,7 @@
         <v>46196</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3">
         <v>0.5</v>
@@ -487,7 +487,7 @@
         <v>46196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3">
         <v>0.5</v>
@@ -498,7 +498,7 @@
         <v>46196</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
@@ -509,7 +509,7 @@
         <v>46196</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -520,7 +520,7 @@
         <v>46198</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>0.5</v>
@@ -531,7 +531,7 @@
         <v>46198</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -542,7 +542,7 @@
         <v>46198</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>0.5</v>
@@ -553,7 +553,7 @@
         <v>46198</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
